--- a/daily_matches/job_matches_2026-10-06.xlsx
+++ b/daily_matches/job_matches_2026-10-06.xlsx
@@ -456,130 +456,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>Network Distribution</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Redshift, BigQuery, Apache Airflow, BigQuery, Redshift</t>
+          <t>Generative AI, RAG, S3, Glue, Data Lake, CI/CD, Terraform, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1d738eb2126f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=271ae7d8ee6706bd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Intern - SMAI TD AI Engineering Team</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Databricks, Kafka, NoSQL</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3904d0205e58da2c</t>
+          <t>https://www.indeed.com/viewjob?jk=9e9f5a8b8e8175b9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Advanced Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>QuadCode</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Azure ML, Data Lake, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Hugging Face, Prompt Engineering, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbab632d0bb04999</t>
+          <t>https://www.indeed.com/viewjob?jk=efb4029a422aab2f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer, Advanced Analytics</t>
+          <t>AI Data Foundation Research Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FastAPI, Kubernetes, CI/CD, Git, Databricks, PySpark, PostgreSQL, Python</t>
+          <t>Generative AI, RAG, LLaMA, TensorFlow, PyTorch, MLflow, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,32 +589,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44ef5d52f3729890</t>
+          <t>https://www.indeed.com/viewjob?jk=d13ddb3e0a52575c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer - (Java/Software Development/AI) - Hybrid</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>bet365</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, GCP Vertex AI, Docker, Kubernetes, CI/CD, Terraform, Kafka, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,102 +624,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9f54f4c0964669</t>
+          <t>https://www.indeed.com/viewjob?jk=e156aa015e45d8c1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Algorithms Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Allied Benefit Systems</t>
+          <t>Keen Decision Systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, Power BI, Python</t>
+          <t>Cortex, FastAPI, Docker, AKS, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2168430383941cce</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ca465482737688</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist, Marketing Analytics</t>
+          <t>Data Engineer – Physical AI Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, scikit-learn, Keras, Git, Databricks, PySpark, Python</t>
+          <t>RAG, S3, Kinesis, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc774e9f722ca0f</t>
+          <t>https://www.indeed.com/viewjob?jk=a8048f9d73fd7da7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 4 - Card Tech</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, Glue, Redshift, CI/CD, Redshift, Tableau, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,67 +729,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b788dde189e4cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=854d296ae3e1537f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Java/ AI Engineer- Cybersecurity Engineer</t>
+          <t>IT Sr. Data Scientist - Clarity &amp; Caboodle</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Prompt Engineering, Docker, AKS, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1063f0338d0013</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7e2a2519c57a47</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Cyber Endpoint Security</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Kafka, NoSQL, Python, SQL, R, Java, C++</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,32 +799,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=768daf548bf7f04f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba230916aa310d2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Software Developer I (Applications and Data)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Barrios Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Docker, Git, PostgreSQL, MySQL, Python, SQL, R, Java, C++, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727d755000763cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec9984509c252eb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4 (ServiceNow)</t>
+          <t>Software Developer I (Applications and Data)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Barrios Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Docker, Git, PostgreSQL, MySQL, Python, SQL, R, Java, C++, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,252 +869,252 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe17e114c2bcc25</t>
+          <t>https://www.indeed.com/viewjob?jk=b014e51870d1ca52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, scikit-learn, AWS SageMaker, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239112321618bfea</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae29b56f69fd7d7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Java, Python, AWS)</t>
+          <t>Sr. Data Analyst, Customer Analytics (Insurance)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, Prompt Engineering, BigQuery, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f20993d5ae69d49</t>
+          <t>https://www.indeed.com/viewjob?jk=2c501b180921cbb7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Applied AI/ML Modeling - Senior Associate</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, scikit-learn, Git, Snowflake, Databricks, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77827d49349dcffa</t>
+          <t>https://www.indeed.com/viewjob?jk=e2686548894b1323</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Git, Python, R, C++, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d562816e08aec62b</t>
+          <t>https://www.indeed.com/viewjob?jk=96a65d878b3a90fc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Software Engineer - Digital Marketing</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>Live Oak Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R</t>
+          <t>RAG, S3, Git, Tableau, Power BI, Python, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd75cc5038cbf242</t>
+          <t>https://www.indeed.com/viewjob?jk=4a3a03e231e77efd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Agentic Product Builder, Sr. Associate - State Street Investment Management</t>
+          <t>Entry-Level AI/ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Git, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, scikit-learn, Git, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474cf3549286b7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=5d359c6b53f8f899</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Engineer, Applications - LATAM</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shoals Technologies Group</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portland, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, CI/CD, Databricks, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82cde14623807d01</t>
+          <t>https://www.indeed.com/viewjob?jk=928a40e135d4f03e</t>
         </is>
       </c>
     </row>
@@ -1126,117 +1126,117 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shoals Technologies Group</t>
+          <t>Spectro Cloud</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portland, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, MongoDB, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=821c9233233a720b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ddd8e63e2b9a1f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (contract)</t>
+          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CoinFlip</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Java</t>
+          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a11c080f7e2d50</t>
+          <t>https://www.indeed.com/viewjob?jk=ac89abd94ee1b3dd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, First Line Risk</t>
+          <t>Especialista /Developer IA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Stefanini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Peru, IN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, BigQuery, Matplotlib, Python, SQL, R</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06dcac8f4983d343</t>
+          <t>https://www.indeed.com/viewjob?jk=047eeb8c7a2f12c2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer, Customer Context</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Postscript</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, Terraform, Kafka, NoSQL, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,24 +1254,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4c0faea6b0d34a</t>
+          <t>https://www.indeed.com/viewjob?jk=1631c2d43eef23fc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer (L2)</t>
+          <t>Applied AI/ML Modeling - Senior Associate</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1279,34 +1279,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, scikit-learn, Git, Snowflake, Databricks, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb75c62e05e399f</t>
+          <t>https://www.indeed.com/viewjob?jk=332fb318c0c1cd35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer</t>
+          <t>Google Cloud AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Silencer Central</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,34 +1314,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, BigQuery, Dataflow, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef720f923ef6dcf8</t>
+          <t>https://www.indeed.com/viewjob?jk=86451a0e98cb7828</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Wireless S/W Engineer</t>
+          <t>Intern - SSD Architecture Modeling</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Python, R, Java, C++, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, R, C++, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,24 +1359,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2672e3e2a931a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=89c5e52b5cfa32de</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Modeler – MAC BI, Activity Intelligence</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Victra-Verizon Authorized Retailer</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, BigQuery, Git, Snowflake, Databricks, BigQuery, SQL, R, Optimization</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,24 +1394,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6095490a0c2adce8</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbd1ecd34ba576b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Bloomington, IL</t>
+          <t>Engineering Internship</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>IDEMIA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Terraform, Git, SQL, R, Java</t>
+          <t>RAG, Docker, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb8484b67761b93</t>
+          <t>https://www.indeed.com/viewjob?jk=f448e092dafb8a67</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-06.xlsx
+++ b/daily_matches/job_matches_2026-10-06.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Data Warehouse / Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Network Distribution</t>
+          <t>KLS Martin Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Glue, Data Lake, CI/CD, Terraform, Git, Snowflake, Python</t>
+          <t>RAG, S3, Glue, Redshift, BigQuery, Synapse, Dataflow, Apache Airflow, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,67 +484,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271ae7d8ee6706bd</t>
+          <t>https://www.indeed.com/viewjob?jk=5d004bc892c60770</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Intern - SMAI TD AI Engineering Team</t>
+          <t>Sr Software Engineer - Digital Banking</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, Python</t>
+          <t>RAG, Prompt Engineering, S3, EC2, Docker, CI/CD, Jenkins, Git, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e9f5a8b8e8175b9</t>
+          <t>https://www.indeed.com/viewjob?jk=acb73e15b88b41b2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr AI/Data Science Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>QuadCode</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Hugging Face, Prompt Engineering, Docker, Kubernetes, Git, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, scikit-learn, AWS SageMaker, MLflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,67 +554,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb4029a422aab2f</t>
+          <t>https://www.indeed.com/viewjob?jk=96bdba5085886da3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Data Foundation Research Engineer</t>
+          <t>Senior AI / ML Engineer - Generative AI &amp; Azure</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, TensorFlow, PyTorch, MLflow, Kubernetes, CI/CD, Git, Python</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Synapse, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d13ddb3e0a52575c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fde5f56dbc38141</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer – Backend</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bet365</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, GCP Vertex AI, Docker, Kubernetes, CI/CD, Terraform, Kafka, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e156aa015e45d8c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ff1e374638f96eca</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Algorithms Engineer</t>
+          <t>Sr. Data Scientist - Commercial</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Keen Decision Systems</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cortex, FastAPI, Docker, AKS, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, scikit-learn, MLflow, CI/CD, Git, Snowflake, Tableau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ca465482737688</t>
+          <t>https://www.indeed.com/viewjob?jk=4ad45f72625bff0a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer – Physical AI Platform</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Kinesis, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Prompt Engineering, S3, Glue, Athena, FastAPI, Terraform, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,59 +694,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8048f9d73fd7da7</t>
+          <t>https://www.indeed.com/viewjob?jk=16e51f89dac07240</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Card Tech</t>
+          <t>Sr Engineer Analytics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854d296ae3e1537f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8a4e4c9e3919f7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT Sr. Data Scientist - Clarity &amp; Caboodle</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,34 +754,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Prompt Engineering, Docker, AKS, Git, Python, SQL, R</t>
+          <t>RAG, FAISS, Pinecone, Data Lake, Kinesis, Kafka, Python, SQL, R, C++</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7e2a2519c57a47</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba7aae9adb38ee</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>HDR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -789,112 +789,112 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Kafka, NoSQL, Python, SQL, R, Java, C++</t>
+          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba230916aa310d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c748dded949b80aa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Developer I (Applications and Data)</t>
+          <t>Software Engineer - Computer Vision &amp; Machine Learning</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Barrios Technology</t>
+          <t>RFA Engineering</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Docker, Git, PostgreSQL, MySQL, Python, SQL, R, Java, C++, Scala</t>
+          <t>TensorFlow, PyTorch, Databricks, Tableau, Matplotlib, Python, SQL, R, C++, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec9984509c252eb</t>
+          <t>https://www.indeed.com/viewjob?jk=045366d755d9d1c8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Developer I (Applications and Data)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Barrios Technology</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Docker, Git, PostgreSQL, MySQL, Python, SQL, R, Java, C++, Scala</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, PyTorch, scikit-learn, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b014e51870d1ca52</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d94abed10dc51f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Scientist I - ML/AI Foundational Models for Synthetic Enhancer Design</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>ALLEN INSTITUTE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, scikit-learn, AWS SageMaker, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, MLflow, Docker, Python, R, Scala, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae29b56f69fd7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=56f047ea2a252151</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst, Customer Analytics (Insurance)</t>
+          <t>Software Engineer, Fleet Engineering</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, BigQuery, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,32 +939,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c501b180921cbb7</t>
+          <t>https://www.indeed.com/viewjob?jk=f9885ce0bd4d7957</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Applied AI/ML Modeling - Senior Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>E2B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, scikit-learn, Git, Snowflake, Databricks, Python, R, Optimization</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,462 +974,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2686548894b1323</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Intuitive (Intuitive Surgical)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Git, Python, R, C++, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96a65d878b3a90fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Digital Marketing</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Live Oak Bank</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Wilmington, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, S3, Git, Tableau, Power BI, Python, R, Scala, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a3a03e231e77efd</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Entry-Level AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>NAVA TECH LLC</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, scikit-learn, Git, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d359c6b53f8f899</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>7-Eleven</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Databricks, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=928a40e135d4f03e</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Spectro Cloud</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, MongoDB, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ddd8e63e2b9a1f</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac89abd94ee1b3dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Especialista /Developer IA</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Stefanini</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Peru, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=047eeb8c7a2f12c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Mastercard</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>O'Fallon, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1631c2d43eef23fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Applied AI/ML Modeling - Senior Associate</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, scikit-learn, Git, Snowflake, Databricks, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=332fb318c0c1cd35</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Google Cloud AI Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, BigQuery, Dataflow, BigQuery, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86451a0e98cb7828</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Intern - SSD Architecture Modeling</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Micron Technology</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, R, C++, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=89c5e52b5cfa32de</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>DevOps Engineer III</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Victra-Verizon Authorized Retailer</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbd1ecd34ba576b</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Engineering Internship</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>IDEMIA</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f448e092dafb8a67</t>
+          <t>https://www.indeed.com/viewjob?jk=dc8f08d2dc6c3368</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-10-06.xlsx
+++ b/daily_matches/job_matches_2026-10-06.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,25 +456,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enterprise Data Warehouse / Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KLS Martin Group</t>
+          <t>Nixon Web Technology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>31.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, BigQuery, Synapse, Dataflow, Apache Airflow, Snowflake, BigQuery</t>
+          <t>Data Scientist, S3, Glue, Redshift, BigQuery, Synapse, Data Lake, Docker, Kubernetes, Apache Airflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -484,32 +484,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d004bc892c60770</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec453d2d16d9041</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Digital Banking</t>
+          <t>Sr Engineer, IT Machine Learning</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>26.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, EC2, Docker, CI/CD, Jenkins, Git, Kafka, Hadoop</t>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone, TensorFlow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -519,32 +519,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb73e15b88b41b2</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9e361c44f6f503</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr AI/Data Science Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>Kroll Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>25.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, TensorFlow, PyTorch, scikit-learn, AWS SageMaker, MLflow</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,67 +554,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bdba5085886da3</t>
+          <t>https://www.indeed.com/viewjob?jk=78b96535deace3b6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI / ML Engineer - Generative AI &amp; Azure</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Novacis Digital</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Synapse, Docker, Kubernetes, AKS</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, ChromaDB, Prompt Engineering</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fde5f56dbc38141</t>
+          <t>https://www.indeed.com/viewjob?jk=0b3d66c67191ca23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RAG, S3, Glue, Redshift, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -624,32 +624,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff1e374638f96eca</t>
+          <t>https://www.indeed.com/viewjob?jk=341da7dee83bcecc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist - Commercial</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, scikit-learn, MLflow, CI/CD, Git, Snowflake, Tableau</t>
+          <t>RAG, S3, Glue, Redshift, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -659,32 +659,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ad45f72625bff0a</t>
+          <t>https://www.indeed.com/viewjob?jk=958b77c45e6daea7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer (Platform)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, S3, Glue, Athena, FastAPI, Terraform, PostgreSQL, Python</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e51f89dac07240</t>
+          <t>https://www.indeed.com/viewjob?jk=75ceb496aa16205b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Engineer Analytics</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Java</t>
+          <t>LangChain, Prompt Engineering, PyTorch, scikit-learn, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,102 +729,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8a4e4c9e3919f7</t>
+          <t>https://www.indeed.com/viewjob?jk=0f35bd1de3b8b37e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Senior AI Ops / DevOps Engineer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, FAISS, Pinecone, Data Lake, Kinesis, Kafka, Python, SQL, R, C++</t>
+          <t>LangChain, RAG, LLaMA, MLflow, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba7aae9adb38ee</t>
+          <t>https://www.indeed.com/viewjob?jk=6415d34be34565d8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cloud Vulnerability Management Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HDR</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c748dded949b80aa</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac0a80ae78e8a3b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer - Computer Vision &amp; Machine Learning</t>
+          <t>AI Solutions Engineer - Associate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RFA Engineering</t>
+          <t>Federal Reserve Bank of Richmond</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Databricks, Tableau, Matplotlib, Python, SQL, R, C++, Optimization</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, S3, EC2, Docker, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=045366d755d9d1c8</t>
+          <t>https://www.indeed.com/viewjob?jk=47786603c2f15c79</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, PyTorch, scikit-learn, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, Generative AI, Copilot, TensorFlow, PyTorch, scikit-learn, Git, Hadoop, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,32 +869,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d94abed10dc51f</t>
+          <t>https://www.indeed.com/viewjob?jk=52df8d0844d029b4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Scientist I - ML/AI Foundational Models for Synthetic Enhancer Design</t>
+          <t>AI Software Engineer Consultant II -</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ALLEN INSTITUTE</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, MLflow, Docker, Python, R, Scala, Optimization, Bayesian</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -904,32 +904,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f047ea2a252151</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1bf92ab09c20bd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer, Fleet Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>MedVet</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, Synapse, Git, Databricks, PySpark, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,42 +939,952 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9885ce0bd4d7957</t>
+          <t>https://www.indeed.com/viewjob?jk=23bae3ccf06adcbd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Foundations</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>E2B</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, FastAPI, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bea612ec37763475</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RAG Arcitect/Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Hugging Face, spaCy, NLTK, Gensim, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b5b4bbbcde64ea7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Support Engineer (Lab Support and Automation)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, CI/CD, Jenkins, Git, PostgreSQL, NoSQL, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4498c014df87f648</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SW Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf136f55dfc88d70</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer - Payment Team</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>San Francisco, CA, US USA</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24357c216e00efd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d42345033b70a0ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern (Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Niantic Spatial</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, OpenCV, Docker, Kubernetes, Terraform, Python, SQL, R, C++</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24e53e340102539a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dealer Tire</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, scikit-learn, Docker, Git, Snowflake, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=204f36c9461521a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dealer Tire</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, scikit-learn, Docker, Git, Snowflake, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=652517920470feb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sr DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Credit Union of Texas</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Allen, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=933f7b241bea8b88</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Autonomy Engineering Specialist - Integrated Technology</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, S3, EC2, Docker, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5f1a6014a630be1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Autonomy Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, S3, EC2, Docker, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e454cf2c4fadde9</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI Vibe Coding Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>VRN Technologies</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eadf67b8f00e2530</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Junior Forward Deployed Engineer(FDE)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>K&amp;k Global Talents</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Milford, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f2a04540e9000eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d32bc60368c3a448</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Modernizing Medicine, Inc.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84ccf0bbab53d85b</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform Engineering</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b77e2e5fec6bdd9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Security Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f493bcc576c8206</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Intermediate Software Engineer (Agentic AI Verification)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Trulioo</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Apache Airflow, Terraform, Git, PySpark, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a25e51451a8d440</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AI Solution Architect - Finance - Remote</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16a1e2041cf9e178</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fusion92</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, scikit-learn, XGBoost, Snowflake, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d86d69fe8d191c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Fusion92</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, scikit-learn, XGBoost, Snowflake, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccb342b00ec6270c</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fusion92</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, scikit-learn, XGBoost, Snowflake, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bfb6dab01762c08</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>REDIANT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb6c759da5962b02</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Multi-Cloud Senior Engineer, Cloud Managed Services</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Presidio</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc8f08d2dc6c3368</t>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, AKS, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3066e4dc57714af8</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GenAI Engineer / Pharma ERP(Raritan, NJ .Hybrid)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>COMPEST SOLUTIONS INDIA PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Raritan, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, CI/CD, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46f4a7ea03c19147</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Detection Engineer, Protective Services</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cb7c0be099cb6b6</t>
         </is>
       </c>
     </row>
